--- a/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
+++ b/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprints" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workload" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sprints" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Team" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Epics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Backlog" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gantt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Workload" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Backlog'!$A$1:$O$212</definedName>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="n">
-        <v>8.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mỗi dev chạy được DB local bằng 1 lệnh; tạo 2 DB role riêng cho backend (schema core) và reco (schema recommendation) như project_architecture.md mục 6. Viết hướng dẫn chạy vào README. Tạo .env.example (backend, reco, frontend) liệt kê đủ key ngoài và tự đăng ký key dùng chung cho dev: Google OAuth ClientId, Brevo ApiKey + sender, Cloudinary (CloudName, ApiKey, ApiSecret), Mapbox secret token (backend) và public token pk.* (frontend), key LLM (reco), X-Api-Key backend ↔ reco. Gửi key cho team qua kênh riêng, không commit (local dùng user-secrets / .env).</t>
+          <t>Mỗi dev chạy được DB local bằng 1 lệnh; tạo 2 DB role riêng cho backend (schema core) và reco (schema recommendation) như project_architecture.md, mục Database. Viết hướng dẫn chạy vào README. Tạo .env.example (backend, reco, frontend) liệt kê đủ key ngoài và tự đăng ký key dùng chung cho dev: Google OAuth ClientId, Brevo ApiKey + sender, Cloudinary (CloudName, ApiKey, ApiSecret), Mapbox secret token (backend) và public token pk.* (frontend), key LLM (reco), X-Api-Key backend ↔ reco. Gửi key cho team qua kênh riêng, không commit (local dùng user-secrets / .env).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Interface ở Application/Common/Interfaces/Services, implementation ở Infrastructure/Services (project_architecture.md mục 2). Dùng cho MEDIA-01 và bảng media_files.</t>
+          <t>Interface ở Application/Common/Interfaces/Services, implementation ở Infrastructure/Services (project_architecture.md, mục Integrations). Dùng cho MEDIA-01 và bảng media_files.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Interface ở Application/Common/Interfaces/Services, implementation ở Infrastructure/Services (project_architecture.md mục 2). Dùng cho F-01, F-02, F-05.</t>
+          <t>Interface ở Application/Common/Interfaces/Services, implementation ở Infrastructure/Services (project_architecture.md, mục Integrations). Dùng cho F-01, F-02, F-05.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Map toàn bộ bảng schema core theo ANGI_Data_Dictionary_Ver1.2 vào ANGIContext (IEntityTypeConfiguration mỗi bảng), BaseEntity + ISoftDelete, enum lưu đúng giá trị chữ thường như sheet Enum của ANGI_API_Design_Ver1.8. Initial migration gồm cả CHECK, citext và trigger outbox (migrationBuilder.Sql). Từ đây schema core chỉ đổi qua EF migration (commit_guide.md mục 10). | Làm sau: Docker Compose môi trường dev: PostgreSQL 16 + pgvector.</t>
+          <t>Map toàn bộ bảng schema core theo ANGI_Data_Dictionary_Ver1.2 vào ANGIContext (IEntityTypeConfiguration mỗi bảng), BaseEntity + ISoftDelete, enum lưu đúng giá trị chữ thường như sheet Enum của ANGI_API_Design_Ver1.8. Initial migration gồm cả CHECK, citext và trigger outbox (migrationBuilder.Sql). Từ đây schema core chỉ đổi qua EF migration (commit_guide.md, mục Migrations). | Làm sau: Docker Compose môi trường dev: PostgreSQL 16 + pgvector.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Mọi response bọc trong ApiResponse&lt;T&gt; (success, message, errorCode, data, errors) theo coding_rule.md mục 5. Middleware map exception sang status + errorCode theo coding_rule.md mục 7 và sheet Mã lỗi của ANGI_API_Design_Ver1.8; 401, 403, 429 và lỗi model binding cũng trả ApiResponse. JWT, CORS, rate limit theo project_architecture.md mục 4–5.</t>
+          <t>Mọi response bọc trong ApiResponse&lt;T&gt; (success, message, errorCode, data, errors) theo coding_rule.md, mục Responses. Middleware map exception sang status + errorCode theo coding_rule.md, mục Errors và sheet Mã lỗi của ANGI_API_Design_Ver1.8; 401, 403, 429 và lỗi model binding cũng trả ApiResponse. JWT, CORS, rate limit theo project_architecture.md, mục Request pipeline và API conventions.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Typed HttpClient gọi RECO-03, RECO-05, RECO-06, RECO-09 với X-Api-Key; timeout 800 ms và fallback xếp theo rating quán (project_architecture.md mục 2). | Làm sau: Khung FastAPI reco service: kết nối schema recommendation, migration, X-Api-Key, /health.</t>
+          <t>Typed HttpClient gọi RECO-03, RECO-05, RECO-06, RECO-09 với X-Api-Key; timeout 800 ms và fallback xếp theo rating quán (project_architecture.md, mục Integrations). | Làm sau: Khung FastAPI reco service: kết nối schema recommendation, migration, X-Api-Key, /health.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="n">
-        <v>8.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
 Endpoint cần làm:
 - HOME-01 GET /api/v1/home
 - IMP-01 POST /api/v1/impressions
-Ghi chú: Món gợi ý lấy qua IRecommendationService (RECO-05). Reco lỗi hoặc quá 800 ms thì xếp theo rating quán (project_architecture.md mục 2). Code trước với bản mock của IRecommendationService (trả lại candidate_dish_ids đúng thứ tự gửi, requestId = null, giống fallback) để không phải chờ RECO-05; reco xong chỉ đổi đăng ký DI. Ứng viên gửi RECO-05 sắp sẵn theo rating trung bình của quán giảm dần, rồi like_count của món giảm dần (reco giữ thứ tự này cho món bằng điểm). Lọc xong còn quá 2000 món thì chỉ gửi 2000 món đầu (RECO-05 nhận tối đa 2000).
+Ghi chú: Món gợi ý lấy qua IRecommendationService (RECO-05). Reco lỗi hoặc quá 800 ms thì xếp theo rating quán (project_architecture.md, mục Integrations). Code trước với bản mock của IRecommendationService (trả lại candidate_dish_ids đúng thứ tự gửi, requestId = null, giống fallback) để không phải chờ RECO-05; reco xong chỉ đổi đăng ký DI. Ứng viên gửi RECO-05 sắp sẵn theo rating trung bình của quán giảm dần, rồi like_count của món giảm dần (reco giữ thứ tự này cho món bằng điểm). Lọc xong còn quá 2000 món thì chỉ gửi 2000 món đầu (RECO-05 nhận tối đa 2000).
 Tài liệu: ANGI_Use_Case_Basic_Descriptions_Ver1.0 (use case), ANGI_API_Design_Ver1.8 (sheet Backend API, Chi tiết Request-Response, Mã lỗi), ANGI_Data_Dictionary_Ver1.2 (bảng), coding_rule.md.
 DoD: Endpoint trả đúng request/response và mã lỗi như ANGI_API_Design_Ver1.8; code theo coding_rule.md; unit test tối thiểu 2 method; hiện trên Scalar; PR được Dũng review. | Làm sau: Reco P1: Cold start (Pooled Wilson) + Content-based, RECO-05 /recommendations, RECO-06 /impressions.</t>
         </is>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>BackgroundService đọc outbox_messages, gửi kèm Idempotency-Key, thử lại theo backoff, chuyển dead khi lỗi 4xx hoặc quá số lần thử. Chi tiết luồng: project_architecture.md mục 7. | Làm sau: Reco P1: Sinh dish vector (RECO-01 upsert, RECO-02 deactivate), [BE] F-50 Manage Restaurant Menu.</t>
+          <t>BackgroundService đọc outbox_messages, gửi kèm Idempotency-Key, thử lại theo backoff, chuyển dead khi lỗi 4xx hoặc quá số lần thử. Chi tiết luồng: project_architecture.md, mục Outbox. | Làm sau: Reco P1: Sinh dish vector (RECO-01 upsert, RECO-02 deactivate), [BE] F-50 Manage Restaurant Menu.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
           <t>[CRITICAL PATH] Task này nằm trên đường găng: dự phòng tối đa 1 ngày. Phải xong đúng Due Date 20/10/2026; trễ 1 ngày thì mốc "Software Package Version 1" (25/10/2026) bị trễ theo.
 Ảnh hưởng trực tiếp tới: Code freeze + tích hợp Iteration 1: merge PR vào dev, chạy toàn hệ thống.
 Gặp vướng thì báo ngay trong ngày cho Dũng (PM), không đợi họp.
-Interface IRouteService ở Application/Common/Interfaces/Services, MapboxRouteService ở Infrastructure/Services (typed HttpClient gọi Mapbox Directions API, 1 lần cho cả ngày, tối đa 25 điểm). Cache IMemoryCache 24 giờ theo profile + tọa độ (điểm xuất phát làm tròn khoảng 100 m); timeout 3 giây, lỗi thì ước lượng đường chim bay × 1,3 và trả isEstimated = true. Tạo tài khoản Mapbox, secret token để ở biến môi trường (Mapbox__AccessToken), public token cho FE. Chi tiết project_architecture.md mục 2 (Map / routing). Dùng cho RM-14 ở F-21 (Iteration 2).</t>
+Interface IRouteService ở Application/Common/Interfaces/Services, MapboxRouteService ở Infrastructure/Services (typed HttpClient gọi Mapbox Directions API, 1 lần cho cả ngày, tối đa 25 điểm). Cache IMemoryCache 24 giờ theo profile + tọa độ (điểm xuất phát làm tròn khoảng 100 m); timeout 3 giây, lỗi thì ước lượng đường chim bay × 1,3 và trả isEstimated = true. Tạo tài khoản Mapbox, secret token để ở biến môi trường (Mapbox__AccessToken), public token cho FE. Chi tiết project_architecture.md, mục Integrations (Mapbox Directions). Dùng cho RM-14 ở F-21 (Iteration 2).</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="n">
-        <v>9.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="M160" s="2" t="inlineStr"/>
       <c r="N160" s="2" t="n">
-        <v>8.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="L2" s="7" t="n"/>
@@ -18701,7 +18701,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
@@ -22139,7 +22139,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>9.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
@@ -25781,7 +25781,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>8.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L160" s="7" t="n"/>
       <c r="M160" s="7" t="n"/>
@@ -28719,6 +28719,7 @@
         <v>99</v>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>

--- a/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
+++ b/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
@@ -15,9 +15,9 @@
     <sheet name="Workload" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Backlog'!$A$1:$O$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Backlog'!$A$1:$O$213</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1359,7 +1359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O212"/>
+  <dimension ref="A1:O213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1515,7 +1515,7 @@
           <t>ANGI-14</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="2"/>
       <c r="N2" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
@@ -1584,7 +1584,7 @@
           <t>ANGI-15</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="M3" s="2"/>
       <c r="N3" s="2" t="n">
         <v>69</v>
       </c>
@@ -1653,7 +1653,7 @@
           <t>ANGI-16</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="M4" s="2"/>
       <c r="N4" s="2" t="n">
         <v>8.5</v>
       </c>
@@ -1722,7 +1722,7 @@
           <t>ANGI-17</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="M5" s="2"/>
       <c r="N5" s="2" t="n">
         <v>11.5</v>
       </c>
@@ -1791,7 +1791,7 @@
           <t>ANGI-18</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="M6" s="2"/>
       <c r="N6" s="2" t="n">
         <v>10.8</v>
       </c>
@@ -1860,7 +1860,7 @@
           <t>ANGI-19</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="M7" s="2"/>
       <c r="N7" s="2" t="n">
         <v>8.1</v>
       </c>
@@ -1929,7 +1929,7 @@
           <t>ANGI-20</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="M8" s="2"/>
       <c r="N8" s="2" t="n">
         <v>8.1</v>
       </c>
@@ -1998,7 +1998,7 @@
           <t>ANGI-21</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="M9" s="2"/>
       <c r="N9" s="2" t="n">
         <v>8.5</v>
       </c>
@@ -2067,7 +2067,7 @@
           <t>ANGI-22</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="M10" s="2"/>
       <c r="N10" s="2" t="n">
         <v>66</v>
       </c>
@@ -2136,7 +2136,7 @@
           <t>ANGI-23</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="M11" s="2"/>
       <c r="N11" s="2" t="n">
         <v>6.4</v>
       </c>
@@ -2205,7 +2205,7 @@
           <t>ANGI-24</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="M12" s="2"/>
       <c r="N12" s="2" t="n">
         <v>65.8</v>
       </c>
@@ -2274,7 +2274,7 @@
           <t>ANGI-25</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="M13" s="2"/>
       <c r="N13" s="2" t="n">
         <v>63</v>
       </c>
@@ -2343,7 +2343,7 @@
           <t>ANGI-26</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="M14" s="2"/>
       <c r="N14" s="2" t="n">
         <v>7.4</v>
       </c>
@@ -2412,7 +2412,7 @@
           <t>ANGI-27</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="M15" s="2"/>
       <c r="N15" s="2" t="n">
         <v>63</v>
       </c>
@@ -2481,7 +2481,7 @@
           <t>ANGI-28</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="M16" s="2"/>
       <c r="N16" s="2" t="n">
         <v>3.1</v>
       </c>
@@ -2555,7 +2555,7 @@
           <t>ANGI-29</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="M17" s="2"/>
       <c r="N17" s="2" t="n">
         <v>7.3</v>
       </c>
@@ -2628,7 +2628,7 @@
           <t>ANGI-30</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="M18" s="2"/>
       <c r="N18" s="2" t="n">
         <v>9.4</v>
       </c>
@@ -2701,7 +2701,7 @@
           <t>ANGI-31</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="M19" s="2"/>
       <c r="N19" s="2" t="n">
         <v>7.2</v>
       </c>
@@ -2770,7 +2770,7 @@
           <t>ANGI-32</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="M20" s="2"/>
       <c r="N20" s="2" t="n">
         <v>5.7</v>
       </c>
@@ -2846,7 +2846,7 @@
           <t>ANGI-33</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="M21" s="2"/>
       <c r="N21" s="2" t="n">
         <v>6.1</v>
       </c>
@@ -2921,7 +2921,7 @@
           <t>ANGI-34</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="M22" s="2"/>
       <c r="N22" s="2" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -2996,7 +2996,7 @@
           <t>ANGI-35</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="M23" s="2"/>
       <c r="N23" s="2" t="n">
         <v>6.7</v>
       </c>
@@ -3070,7 +3070,7 @@
           <t>ANGI-36</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="M24" s="2"/>
       <c r="N24" s="2" t="n">
         <v>8.9</v>
       </c>
@@ -3139,7 +3139,7 @@
           <t>ANGI-37</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="M25" s="2"/>
       <c r="N25" s="2" t="n">
         <v>2.4</v>
       </c>
@@ -3214,7 +3214,7 @@
           <t>ANGI-38</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="M26" s="2"/>
       <c r="N26" s="2" t="n">
         <v>6.1</v>
       </c>
@@ -3288,7 +3288,7 @@
           <t>ANGI-39</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="M27" s="2"/>
       <c r="N27" s="2" t="n">
         <v>6</v>
       </c>
@@ -3362,7 +3362,7 @@
           <t>ANGI-40</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="M28" s="2"/>
       <c r="N28" s="2" t="n">
         <v>5.8</v>
       </c>
@@ -3435,7 +3435,7 @@
           <t>ANGI-41</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="M29" s="2"/>
       <c r="N29" s="2" t="n">
         <v>7.8</v>
       </c>
@@ -3509,7 +3509,7 @@
           <t>ANGI-42</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="M30" s="2"/>
       <c r="N30" s="2" t="n">
         <v>5.4</v>
       </c>
@@ -3583,7 +3583,7 @@
           <t>ANGI-43</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
+      <c r="M31" s="2"/>
       <c r="N31" s="2" t="n">
         <v>7.8</v>
       </c>
@@ -3652,7 +3652,7 @@
           <t>ANGI-44</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="M32" s="2"/>
       <c r="N32" s="2" t="n">
         <v>2.4</v>
       </c>
@@ -3721,7 +3721,7 @@
           <t>ANGI-45</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="M33" s="2"/>
       <c r="N33" s="2" t="n">
         <v>60</v>
       </c>
@@ -3796,7 +3796,7 @@
           <t>ANGI-46</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="M34" s="2"/>
       <c r="N34" s="2" t="n">
         <v>7.1</v>
       </c>
@@ -3869,7 +3869,7 @@
           <t>ANGI-47</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="M35" s="2"/>
       <c r="N35" s="2" t="n">
         <v>5.3</v>
       </c>
@@ -3942,7 +3942,7 @@
           <t>ANGI-48</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="M36" s="2"/>
       <c r="N36" s="2" t="n">
         <v>7</v>
       </c>
@@ -4015,7 +4015,7 @@
           <t>ANGI-49</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="M37" s="2"/>
       <c r="N37" s="2" t="n">
         <v>5</v>
       </c>
@@ -4167,7 +4167,7 @@
           <t>ANGI-51</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="M39" s="2"/>
       <c r="N39" s="2" t="n">
         <v>6.5</v>
       </c>
@@ -4240,7 +4240,7 @@
           <t>ANGI-52</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="M40" s="2"/>
       <c r="N40" s="2" t="n">
         <v>4.8</v>
       </c>
@@ -4322,7 +4322,7 @@
           <t>ANGI-53</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="M41" s="2"/>
       <c r="N41" s="2" t="n">
         <v>4.3</v>
       </c>
@@ -4395,7 +4395,7 @@
           <t>ANGI-54</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="M42" s="2"/>
       <c r="N42" s="2" t="n">
         <v>6.1</v>
       </c>
@@ -4468,7 +4468,7 @@
           <t>ANGI-55</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="M43" s="2"/>
       <c r="N43" s="2" t="n">
         <v>6.6</v>
       </c>
@@ -4541,7 +4541,7 @@
           <t>ANGI-56</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2"/>
       <c r="N44" s="2" t="n">
         <v>4.2</v>
       </c>
@@ -4693,7 +4693,7 @@
           <t>ANGI-58</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="M46" s="2"/>
       <c r="N46" s="2" t="n">
         <v>3.8</v>
       </c>
@@ -4767,7 +4767,7 @@
           <t>ANGI-59</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
+      <c r="M47" s="2"/>
       <c r="N47" s="2" t="n">
         <v>5.8</v>
       </c>
@@ -4840,7 +4840,7 @@
           <t>ANGI-60</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr"/>
+      <c r="M48" s="2"/>
       <c r="N48" s="2" t="n">
         <v>3.7</v>
       </c>
@@ -4914,7 +4914,7 @@
           <t>ANGI-61</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr"/>
+      <c r="M49" s="2"/>
       <c r="N49" s="2" t="n">
         <v>5.5</v>
       </c>
@@ -4988,7 +4988,7 @@
           <t>ANGI-62</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr"/>
+      <c r="M50" s="2"/>
       <c r="N50" s="2" t="n">
         <v>3.2</v>
       </c>
@@ -5061,7 +5061,7 @@
           <t>ANGI-63</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
+      <c r="M51" s="2"/>
       <c r="N51" s="2" t="n">
         <v>5.2</v>
       </c>
@@ -5135,7 +5135,7 @@
           <t>ANGI-64</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="M52" s="2"/>
       <c r="N52" s="2" t="n">
         <v>3.4</v>
       </c>
@@ -5208,7 +5208,7 @@
           <t>ANGI-65</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr"/>
+      <c r="M53" s="2"/>
       <c r="N53" s="2" t="n">
         <v>5.1</v>
       </c>
@@ -5282,7 +5282,7 @@
           <t>ANGI-66</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr"/>
+      <c r="M54" s="2"/>
       <c r="N54" s="2" t="n">
         <v>2.8</v>
       </c>
@@ -5356,7 +5356,7 @@
           <t>ANGI-67</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr"/>
+      <c r="M55" s="2"/>
       <c r="N55" s="2" t="n">
         <v>4.9</v>
       </c>
@@ -5429,7 +5429,7 @@
           <t>ANGI-68</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="M56" s="2"/>
       <c r="N56" s="2" t="n">
         <v>4.4</v>
       </c>
@@ -5587,7 +5587,7 @@
           <t>ANGI-70</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="M58" s="2"/>
       <c r="N58" s="2" t="n">
         <v>2.3</v>
       </c>
@@ -5662,7 +5662,7 @@
           <t>ANGI-71</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr"/>
+      <c r="M59" s="2"/>
       <c r="N59" s="2" t="n">
         <v>2</v>
       </c>
@@ -5821,7 +5821,7 @@
           <t>ANGI-73</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr"/>
+      <c r="M61" s="2"/>
       <c r="N61" s="2" t="n">
         <v>3.9</v>
       </c>
@@ -5896,7 +5896,7 @@
           <t>ANGI-74</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="M62" s="2"/>
       <c r="N62" s="2" t="n">
         <v>3.6</v>
       </c>
@@ -5970,7 +5970,7 @@
           <t>ANGI-75</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="M63" s="2"/>
       <c r="N63" s="2" t="n">
         <v>1.7</v>
       </c>
@@ -6120,7 +6120,7 @@
           <t>ANGI-77</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr"/>
+      <c r="M65" s="2"/>
       <c r="N65" s="2" t="n">
         <v>3</v>
       </c>
@@ -6276,7 +6276,7 @@
           <t>ANGI-79</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr"/>
+      <c r="M67" s="2"/>
       <c r="N67" s="2" t="n">
         <v>2.9</v>
       </c>
@@ -6357,7 +6357,7 @@
           <t>ANGI-80</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr"/>
+      <c r="M68" s="2"/>
       <c r="N68" s="2" t="n">
         <v>1.8</v>
       </c>
@@ -6430,7 +6430,7 @@
           <t>ANGI-81</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr"/>
+      <c r="M69" s="2"/>
       <c r="N69" s="2" t="n">
         <v>2.6</v>
       </c>
@@ -6503,7 +6503,7 @@
           <t>ANGI-82</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="M70" s="2"/>
       <c r="N70" s="2" t="n">
         <v>2.3</v>
       </c>
@@ -6652,7 +6652,7 @@
           <t>ANGI-83</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr"/>
+      <c r="M72" s="2"/>
       <c r="N72" s="2" t="n">
         <v>1.6</v>
       </c>
@@ -6721,7 +6721,7 @@
           <t>ANGI-84</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr"/>
+      <c r="M73" s="2"/>
       <c r="N73" s="2" t="n">
         <v>4</v>
       </c>
@@ -6955,7 +6955,7 @@
           <t>ANGI-87</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr"/>
+      <c r="M76" s="2"/>
       <c r="N76" s="2" t="n">
         <v>54</v>
       </c>
@@ -7634,7 +7634,7 @@
           <t>ANGI-96</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr"/>
+      <c r="M85" s="2"/>
       <c r="N85" s="2" t="n">
         <v>8.5</v>
       </c>
@@ -7703,7 +7703,7 @@
           <t>ANGI-97</t>
         </is>
       </c>
-      <c r="M86" s="2" t="inlineStr"/>
+      <c r="M86" s="2"/>
       <c r="N86" s="2" t="n">
         <v>50</v>
       </c>
@@ -7853,7 +7853,7 @@
           <t>ANGI-99</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr"/>
+      <c r="M88" s="2"/>
       <c r="N88" s="2" t="n">
         <v>7.5</v>
       </c>
@@ -7927,7 +7927,7 @@
           <t>ANGI-100</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr"/>
+      <c r="M89" s="2"/>
       <c r="N89" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
@@ -8000,7 +8000,7 @@
           <t>ANGI-101</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr"/>
+      <c r="M90" s="2"/>
       <c r="N90" s="2" t="n">
         <v>7.3</v>
       </c>
@@ -8069,7 +8069,7 @@
           <t>ANGI-102</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr"/>
+      <c r="M91" s="2"/>
       <c r="N91" s="2" t="n">
         <v>6.3</v>
       </c>
@@ -8142,7 +8142,7 @@
           <t>ANGI-103</t>
         </is>
       </c>
-      <c r="M92" s="2" t="inlineStr"/>
+      <c r="M92" s="2"/>
       <c r="N92" s="2" t="n">
         <v>8.9</v>
       </c>
@@ -8217,7 +8217,7 @@
           <t>ANGI-104</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr"/>
+      <c r="M93" s="2"/>
       <c r="N93" s="2" t="n">
         <v>3.9</v>
       </c>
@@ -8292,7 +8292,7 @@
           <t>ANGI-105</t>
         </is>
       </c>
-      <c r="M94" s="2" t="inlineStr"/>
+      <c r="M94" s="2"/>
       <c r="N94" s="2" t="n">
         <v>8.5</v>
       </c>
@@ -8366,7 +8366,7 @@
           <t>ANGI-106</t>
         </is>
       </c>
-      <c r="M95" s="2" t="inlineStr"/>
+      <c r="M95" s="2"/>
       <c r="N95" s="2" t="n">
         <v>6</v>
       </c>
@@ -8439,7 +8439,7 @@
           <t>ANGI-107</t>
         </is>
       </c>
-      <c r="M96" s="2" t="inlineStr"/>
+      <c r="M96" s="2"/>
       <c r="N96" s="2" t="n">
         <v>6.1</v>
       </c>
@@ -8508,7 +8508,7 @@
           <t>ANGI-108</t>
         </is>
       </c>
-      <c r="M97" s="2" t="inlineStr"/>
+      <c r="M97" s="2"/>
       <c r="N97" s="2" t="n">
         <v>6.3</v>
       </c>
@@ -8581,7 +8581,7 @@
           <t>ANGI-109</t>
         </is>
       </c>
-      <c r="M98" s="2" t="inlineStr"/>
+      <c r="M98" s="2"/>
       <c r="N98" s="2" t="n">
         <v>6</v>
       </c>
@@ -8654,7 +8654,7 @@
           <t>ANGI-110</t>
         </is>
       </c>
-      <c r="M99" s="2" t="inlineStr"/>
+      <c r="M99" s="2"/>
       <c r="N99" s="2" t="n">
         <v>8</v>
       </c>
@@ -8728,7 +8728,7 @@
           <t>ANGI-111</t>
         </is>
       </c>
-      <c r="M100" s="2" t="inlineStr"/>
+      <c r="M100" s="2"/>
       <c r="N100" s="2" t="n">
         <v>5.6</v>
       </c>
@@ -8802,7 +8802,7 @@
           <t>ANGI-112</t>
         </is>
       </c>
-      <c r="M101" s="2" t="inlineStr"/>
+      <c r="M101" s="2"/>
       <c r="N101" s="2" t="n">
         <v>7.8</v>
       </c>
@@ -8871,7 +8871,7 @@
           <t>ANGI-113</t>
         </is>
       </c>
-      <c r="M102" s="2" t="inlineStr"/>
+      <c r="M102" s="2"/>
       <c r="N102" s="2" t="n">
         <v>46</v>
       </c>
@@ -8946,7 +8946,7 @@
           <t>ANGI-114</t>
         </is>
       </c>
-      <c r="M103" s="2" t="inlineStr"/>
+      <c r="M103" s="2"/>
       <c r="N103" s="2" t="n">
         <v>5.1</v>
       </c>
@@ -9021,7 +9021,7 @@
           <t>ANGI-115</t>
         </is>
       </c>
-      <c r="M104" s="2" t="inlineStr"/>
+      <c r="M104" s="2"/>
       <c r="N104" s="2" t="n">
         <v>7.1</v>
       </c>
@@ -9094,7 +9094,7 @@
           <t>ANGI-116</t>
         </is>
       </c>
-      <c r="M105" s="2" t="inlineStr"/>
+      <c r="M105" s="2"/>
       <c r="N105" s="2" t="n">
         <v>7.1</v>
       </c>
@@ -9167,7 +9167,7 @@
           <t>ANGI-117</t>
         </is>
       </c>
-      <c r="M106" s="2" t="inlineStr"/>
+      <c r="M106" s="2"/>
       <c r="N106" s="2" t="n">
         <v>5.1</v>
       </c>
@@ -9240,7 +9240,7 @@
           <t>ANGI-118</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr"/>
+      <c r="M107" s="2"/>
       <c r="N107" s="2" t="n">
         <v>4.8</v>
       </c>
@@ -9313,7 +9313,7 @@
           <t>ANGI-119</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr"/>
+      <c r="M108" s="2"/>
       <c r="N108" s="2" t="n">
         <v>6.8</v>
       </c>
@@ -9387,7 +9387,7 @@
           <t>ANGI-120</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr"/>
+      <c r="M109" s="2"/>
       <c r="N109" s="2" t="n">
         <v>6.4</v>
       </c>
@@ -9460,7 +9460,7 @@
           <t>ANGI-121</t>
         </is>
       </c>
-      <c r="M110" s="2" t="inlineStr"/>
+      <c r="M110" s="2"/>
       <c r="N110" s="2" t="n">
         <v>4.6</v>
       </c>
@@ -9529,7 +9529,7 @@
           <t>ANGI-122</t>
         </is>
       </c>
-      <c r="M111" s="2" t="inlineStr"/>
+      <c r="M111" s="2"/>
       <c r="N111" s="2" t="n">
         <v>6.3</v>
       </c>
@@ -9602,7 +9602,7 @@
           <t>ANGI-123</t>
         </is>
       </c>
-      <c r="M112" s="2" t="inlineStr"/>
+      <c r="M112" s="2"/>
       <c r="N112" s="2" t="n">
         <v>4.4</v>
       </c>
@@ -9677,7 +9677,7 @@
           <t>ANGI-124</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr"/>
+      <c r="M113" s="2"/>
       <c r="N113" s="2" t="n">
         <v>3.3</v>
       </c>
@@ -9751,7 +9751,7 @@
           <t>ANGI-125</t>
         </is>
       </c>
-      <c r="M114" s="2" t="inlineStr"/>
+      <c r="M114" s="2"/>
       <c r="N114" s="2" t="n">
         <v>5.9</v>
       </c>
@@ -9824,7 +9824,7 @@
           <t>ANGI-126</t>
         </is>
       </c>
-      <c r="M115" s="2" t="inlineStr"/>
+      <c r="M115" s="2"/>
       <c r="N115" s="2" t="n">
         <v>5.7</v>
       </c>
@@ -9900,7 +9900,7 @@
           <t>ANGI-127</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr"/>
+      <c r="M116" s="2"/>
       <c r="N116" s="2" t="n">
         <v>3.9</v>
       </c>
@@ -9975,7 +9975,7 @@
           <t>ANGI-128</t>
         </is>
       </c>
-      <c r="M117" s="2" t="inlineStr"/>
+      <c r="M117" s="2"/>
       <c r="N117" s="2" t="n">
         <v>1.7</v>
       </c>
@@ -10049,7 +10049,7 @@
           <t>ANGI-129</t>
         </is>
       </c>
-      <c r="M118" s="2" t="inlineStr"/>
+      <c r="M118" s="2"/>
       <c r="N118" s="2" t="n">
         <v>3.3</v>
       </c>
@@ -10123,7 +10123,7 @@
           <t>ANGI-130</t>
         </is>
       </c>
-      <c r="M119" s="2" t="inlineStr"/>
+      <c r="M119" s="2"/>
       <c r="N119" s="2" t="n">
         <v>5.4</v>
       </c>
@@ -10197,7 +10197,7 @@
           <t>ANGI-131</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr"/>
+      <c r="M120" s="2"/>
       <c r="N120" s="2" t="n">
         <v>3.2</v>
       </c>
@@ -10270,7 +10270,7 @@
           <t>ANGI-132</t>
         </is>
       </c>
-      <c r="M121" s="2" t="inlineStr"/>
+      <c r="M121" s="2"/>
       <c r="N121" s="2" t="n">
         <v>2.1</v>
       </c>
@@ -10343,7 +10343,7 @@
           <t>ANGI-133</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr"/>
+      <c r="M122" s="2"/>
       <c r="N122" s="2" t="n">
         <v>4.8</v>
       </c>
@@ -10416,7 +10416,7 @@
           <t>ANGI-134</t>
         </is>
       </c>
-      <c r="M123" s="2" t="inlineStr"/>
+      <c r="M123" s="2"/>
       <c r="N123" s="2" t="n">
         <v>5</v>
       </c>
@@ -10489,7 +10489,7 @@
           <t>ANGI-135</t>
         </is>
       </c>
-      <c r="M124" s="2" t="inlineStr"/>
+      <c r="M124" s="2"/>
       <c r="N124" s="2" t="n">
         <v>2.7</v>
       </c>
@@ -10562,7 +10562,7 @@
           <t>ANGI-136</t>
         </is>
       </c>
-      <c r="M125" s="2" t="inlineStr"/>
+      <c r="M125" s="2"/>
       <c r="N125" s="2" t="n">
         <v>4.6</v>
       </c>
@@ -10716,7 +10716,7 @@
           <t>ANGI-138</t>
         </is>
       </c>
-      <c r="M127" s="2" t="inlineStr"/>
+      <c r="M127" s="2"/>
       <c r="N127" s="2" t="n">
         <v>3.3</v>
       </c>
@@ -10790,7 +10790,7 @@
           <t>ANGI-139</t>
         </is>
       </c>
-      <c r="M128" s="2" t="inlineStr"/>
+      <c r="M128" s="2"/>
       <c r="N128" s="2" t="n">
         <v>1.9</v>
       </c>
@@ -10866,7 +10866,7 @@
           <t>ANGI-140</t>
         </is>
       </c>
-      <c r="M129" s="2" t="inlineStr"/>
+      <c r="M129" s="2"/>
       <c r="N129" s="2" t="n">
         <v>3.9</v>
       </c>
@@ -11182,7 +11182,7 @@
           <t>ANGI-144</t>
         </is>
       </c>
-      <c r="M133" s="2" t="inlineStr"/>
+      <c r="M133" s="2"/>
       <c r="N133" s="2" t="n">
         <v>1.6</v>
       </c>
@@ -11256,7 +11256,7 @@
           <t>ANGI-145</t>
         </is>
       </c>
-      <c r="M134" s="2" t="inlineStr"/>
+      <c r="M134" s="2"/>
       <c r="N134" s="2" t="n">
         <v>3.2</v>
       </c>
@@ -11412,7 +11412,7 @@
           <t>ANGI-147</t>
         </is>
       </c>
-      <c r="M136" s="2" t="inlineStr"/>
+      <c r="M136" s="2"/>
       <c r="N136" s="2" t="n">
         <v>2.5</v>
       </c>
@@ -11485,7 +11485,7 @@
           <t>ANGI-148</t>
         </is>
       </c>
-      <c r="M137" s="2" t="inlineStr"/>
+      <c r="M137" s="2"/>
       <c r="N137" s="2" t="n">
         <v>2.8</v>
       </c>
@@ -11558,7 +11558,7 @@
           <t>ANGI-149</t>
         </is>
       </c>
-      <c r="M138" s="2" t="inlineStr"/>
+      <c r="M138" s="2"/>
       <c r="N138" s="2" t="n">
         <v>2.2</v>
       </c>
@@ -11631,7 +11631,7 @@
           <t>ANGI-150</t>
         </is>
       </c>
-      <c r="M139" s="2" t="inlineStr"/>
+      <c r="M139" s="2"/>
       <c r="N139" s="2" t="n">
         <v>2.1</v>
       </c>
@@ -11787,7 +11787,7 @@
           <t>ANGI-152</t>
         </is>
       </c>
-      <c r="M141" s="2" t="inlineStr"/>
+      <c r="M141" s="2"/>
       <c r="N141" s="2" t="n">
         <v>1.6</v>
       </c>
@@ -12020,7 +12020,7 @@
           <t>ANGI-155</t>
         </is>
       </c>
-      <c r="M144" s="2" t="inlineStr"/>
+      <c r="M144" s="2"/>
       <c r="N144" s="2" t="n">
         <v>40</v>
       </c>
@@ -12699,7 +12699,7 @@
           <t>ANGI-164</t>
         </is>
       </c>
-      <c r="M153" s="2" t="inlineStr"/>
+      <c r="M153" s="2"/>
       <c r="N153" s="2" t="n">
         <v>8</v>
       </c>
@@ -12768,7 +12768,7 @@
           <t>ANGI-165</t>
         </is>
       </c>
-      <c r="M154" s="2" t="inlineStr"/>
+      <c r="M154" s="2"/>
       <c r="N154" s="2" t="n">
         <v>36</v>
       </c>
@@ -12918,7 +12918,7 @@
           <t>ANGI-167</t>
         </is>
       </c>
-      <c r="M156" s="2" t="inlineStr"/>
+      <c r="M156" s="2"/>
       <c r="N156" s="2" t="n">
         <v>7.4</v>
       </c>
@@ -12992,7 +12992,7 @@
           <t>ANGI-168</t>
         </is>
       </c>
-      <c r="M157" s="2" t="inlineStr"/>
+      <c r="M157" s="2"/>
       <c r="N157" s="2" t="n">
         <v>8.6</v>
       </c>
@@ -13068,7 +13068,7 @@
           <t>ANGI-169</t>
         </is>
       </c>
-      <c r="M158" s="2" t="inlineStr"/>
+      <c r="M158" s="2"/>
       <c r="N158" s="2" t="n">
         <v>6.4</v>
       </c>
@@ -13145,7 +13145,7 @@
           <t>ANGI-170</t>
         </is>
       </c>
-      <c r="M159" s="2" t="inlineStr"/>
+      <c r="M159" s="2"/>
       <c r="N159" s="2" t="n">
         <v>4.7</v>
       </c>
@@ -13221,7 +13221,7 @@
           <t>ANGI-171</t>
         </is>
       </c>
-      <c r="M160" s="2" t="inlineStr"/>
+      <c r="M160" s="2"/>
       <c r="N160" s="2" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -13290,7 +13290,7 @@
           <t>ANGI-172</t>
         </is>
       </c>
-      <c r="M161" s="2" t="inlineStr"/>
+      <c r="M161" s="2"/>
       <c r="N161" s="2" t="n">
         <v>4.9</v>
       </c>
@@ -13364,7 +13364,7 @@
           <t>ANGI-173</t>
         </is>
       </c>
-      <c r="M162" s="2" t="inlineStr"/>
+      <c r="M162" s="2"/>
       <c r="N162" s="2" t="n">
         <v>5.5</v>
       </c>
@@ -13440,7 +13440,7 @@
           <t>ANGI-174</t>
         </is>
       </c>
-      <c r="M163" s="2" t="inlineStr"/>
+      <c r="M163" s="2"/>
       <c r="N163" s="2" t="n">
         <v>7.2</v>
       </c>
@@ -13516,7 +13516,7 @@
           <t>ANGI-175</t>
         </is>
       </c>
-      <c r="M164" s="2" t="inlineStr"/>
+      <c r="M164" s="2"/>
       <c r="N164" s="2" t="n">
         <v>5.3</v>
       </c>
@@ -13592,7 +13592,7 @@
           <t>ANGI-176</t>
         </is>
       </c>
-      <c r="M165" s="2" t="inlineStr"/>
+      <c r="M165" s="2"/>
       <c r="N165" s="2" t="n">
         <v>7.7</v>
       </c>
@@ -13661,7 +13661,7 @@
           <t>ANGI-177</t>
         </is>
       </c>
-      <c r="M166" s="2" t="inlineStr"/>
+      <c r="M166" s="2"/>
       <c r="N166" s="2" t="n">
         <v>32</v>
       </c>
@@ -13736,7 +13736,7 @@
           <t>ANGI-178</t>
         </is>
       </c>
-      <c r="M167" s="2" t="inlineStr"/>
+      <c r="M167" s="2"/>
       <c r="N167" s="2" t="n">
         <v>4.3</v>
       </c>
@@ -13812,7 +13812,7 @@
           <t>ANGI-179</t>
         </is>
       </c>
-      <c r="M168" s="2" t="inlineStr"/>
+      <c r="M168" s="2"/>
       <c r="N168" s="2" t="n">
         <v>4.8</v>
       </c>
@@ -13886,7 +13886,7 @@
           <t>ANGI-180</t>
         </is>
       </c>
-      <c r="M169" s="2" t="inlineStr"/>
+      <c r="M169" s="2"/>
       <c r="N169" s="2" t="n">
         <v>5.8</v>
       </c>
@@ -13962,7 +13962,7 @@
           <t>ANGI-181</t>
         </is>
       </c>
-      <c r="M170" s="2" t="inlineStr"/>
+      <c r="M170" s="2"/>
       <c r="N170" s="2" t="n">
         <v>5.7</v>
       </c>
@@ -14035,7 +14035,7 @@
           <t>ANGI-182</t>
         </is>
       </c>
-      <c r="M171" s="2" t="inlineStr"/>
+      <c r="M171" s="2"/>
       <c r="N171" s="2" t="n">
         <v>4.5</v>
       </c>
@@ -14110,7 +14110,7 @@
           <t>ANGI-183</t>
         </is>
       </c>
-      <c r="M172" s="2" t="inlineStr"/>
+      <c r="M172" s="2"/>
       <c r="N172" s="2" t="n">
         <v>3.9</v>
       </c>
@@ -14187,7 +14187,7 @@
           <t>ANGI-184</t>
         </is>
       </c>
-      <c r="M173" s="2" t="inlineStr"/>
+      <c r="M173" s="2"/>
       <c r="N173" s="2" t="n">
         <v>2.7</v>
       </c>
@@ -14256,7 +14256,7 @@
           <t>ANGI-185</t>
         </is>
       </c>
-      <c r="M174" s="2" t="inlineStr"/>
+      <c r="M174" s="2"/>
       <c r="N174" s="2" t="n">
         <v>4.9</v>
       </c>
@@ -14329,7 +14329,7 @@
           <t>ANGI-186</t>
         </is>
       </c>
-      <c r="M175" s="2" t="inlineStr"/>
+      <c r="M175" s="2"/>
       <c r="N175" s="2" t="n">
         <v>3.2</v>
       </c>
@@ -14405,7 +14405,7 @@
           <t>ANGI-187</t>
         </is>
       </c>
-      <c r="M176" s="2" t="inlineStr"/>
+      <c r="M176" s="2"/>
       <c r="N176" s="2" t="n">
         <v>4.5</v>
       </c>
@@ -14479,7 +14479,7 @@
           <t>ANGI-188</t>
         </is>
       </c>
-      <c r="M177" s="2" t="inlineStr"/>
+      <c r="M177" s="2"/>
       <c r="N177" s="2" t="n">
         <v>4.9</v>
       </c>
@@ -14556,7 +14556,7 @@
           <t>ANGI-189</t>
         </is>
       </c>
-      <c r="M178" s="2" t="inlineStr"/>
+      <c r="M178" s="2"/>
       <c r="N178" s="2" t="n">
         <v>1.6</v>
       </c>
@@ -14629,7 +14629,7 @@
           <t>ANGI-190</t>
         </is>
       </c>
-      <c r="M179" s="2" t="inlineStr"/>
+      <c r="M179" s="2"/>
       <c r="N179" s="2" t="n">
         <v>3.8</v>
       </c>
@@ -14706,7 +14706,7 @@
           <t>ANGI-191</t>
         </is>
       </c>
-      <c r="M180" s="2" t="inlineStr"/>
+      <c r="M180" s="2"/>
       <c r="N180" s="2" t="n">
         <v>2</v>
       </c>
@@ -14781,7 +14781,7 @@
           <t>ANGI-192</t>
         </is>
       </c>
-      <c r="M181" s="2" t="inlineStr"/>
+      <c r="M181" s="2"/>
       <c r="N181" s="2" t="n">
         <v>3.7</v>
       </c>
@@ -14850,7 +14850,7 @@
           <t>ANGI-193</t>
         </is>
       </c>
-      <c r="M182" s="2" t="inlineStr"/>
+      <c r="M182" s="2"/>
       <c r="N182" s="2" t="n">
         <v>3</v>
       </c>
@@ -15090,7 +15090,7 @@
           <t>ANGI-196</t>
         </is>
       </c>
-      <c r="M185" s="2" t="inlineStr"/>
+      <c r="M185" s="2"/>
       <c r="N185" s="2" t="n">
         <v>2.6</v>
       </c>
@@ -15165,7 +15165,7 @@
           <t>ANGI-197</t>
         </is>
       </c>
-      <c r="M186" s="2" t="inlineStr"/>
+      <c r="M186" s="2"/>
       <c r="N186" s="2" t="n">
         <v>2.4</v>
       </c>
@@ -15324,7 +15324,7 @@
           <t>ANGI-199</t>
         </is>
       </c>
-      <c r="M188" s="2" t="inlineStr"/>
+      <c r="M188" s="2"/>
       <c r="N188" s="2" t="n">
         <v>1.8</v>
       </c>
@@ -15478,7 +15478,7 @@
           <t>ANGI-201</t>
         </is>
       </c>
-      <c r="M190" s="2" t="inlineStr"/>
+      <c r="M190" s="2"/>
       <c r="N190" s="2" t="n">
         <v>26</v>
       </c>
@@ -16772,7 +16772,7 @@
           <t>ANGI-218</t>
         </is>
       </c>
-      <c r="M207" s="2" t="inlineStr"/>
+      <c r="M207" s="2"/>
       <c r="N207" s="2" t="n">
         <v>12</v>
       </c>
@@ -16841,7 +16841,7 @@
           <t>ANGI-219</t>
         </is>
       </c>
-      <c r="M208" s="2" t="inlineStr"/>
+      <c r="M208" s="2"/>
       <c r="N208" s="2" t="n">
         <v>2</v>
       </c>
@@ -17158,8 +17158,67 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T231</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BE] Implement Agent roadmap conversations MVP</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implement AGENT-01..04 from ANGI_Agent_Implementation_Ver1.1: expiring memory, leased/idempotent turns, scoped validated proposals, atomic create/update confirmation, roadmap revisions, cleanup and tests. API/Data Dictionary additions accompany source. Refs: ANGI-231.</t>
+        </is>
+      </c>
+      <c r="E213" s="2">
+      </c>
+      <c r="F213" s="2">
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EP-ROAD</t>
+        </is>
+      </c>
+      <c r="H213" s="2">
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/10/2026</t>
+        </is>
+      </c>
+      <c r="J213" s="2">
+      </c>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend agent roadmap</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGI-231</t>
+        </is>
+      </c>
+      <c r="M213" s="2">
+      </c>
+      <c r="N213" s="2">
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O212"/>
+  <autoFilter ref="A1:O213"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17170,7 +17229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX212"/>
+  <dimension ref="A1:BX213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28513,6 +28572,71 @@
       <c r="BW212" s="9" t="n"/>
       <c r="BX212" s="9" t="n"/>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGI-231</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BE] Implement Agent roadmap conversations MVP</t>
+        </is>
+      </c>
+      <c r="C213">
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26/10/2026</t>
+        </is>
+      </c>
+      <c r="E213">
+      </c>
+      <c r="F213">
+      </c>
+      <c r="G213">
+      </c>
+      <c r="L213" s="7">
+      </c>
+      <c r="M213" s="7">
+      </c>
+      <c r="S213" s="7">
+      </c>
+      <c r="T213" s="7">
+      </c>
+      <c r="Z213" s="7">
+      </c>
+      <c r="AA213" s="7">
+      </c>
+      <c r="AG213" s="7">
+      </c>
+      <c r="AH213" s="7">
+      </c>
+      <c r="AN213" s="7">
+      </c>
+      <c r="AO213" s="7">
+      </c>
+      <c r="AU213" s="7">
+      </c>
+      <c r="AV213" s="7">
+      </c>
+      <c r="BB213" s="7">
+      </c>
+      <c r="BC213" s="7">
+      </c>
+      <c r="BI213" s="7">
+      </c>
+      <c r="BJ213" s="7">
+      </c>
+      <c r="BP213" s="7">
+      </c>
+      <c r="BQ213" s="7">
+      </c>
+      <c r="BW213" s="7">
+      </c>
+      <c r="BX213" s="7">
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28524,7 +28648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -28719,7 +28843,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+    </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>

--- a/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
+++ b/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Dữ liệu đúng cấu trúc ANGI_Data_Dictionary_Ver1.2, chạy lại được nhiều lần. Đủ để test Discovery và Roadmap trước khi có Moderation (Iteration 3); mỗi role có ít nhất 1 tài khoản test. Mọi quán phải có tọa độ thật (latitude/longitude bắt buộc); mỗi tỉnh test có quán ở vài quận khác nhau để thử lọc quán gần, gom cụm theo ngày và route Mapbox. Mỗi món có mô tả rõ vị (30..2000 ký tự) vì reco sinh dish vector từ tên + mô tả. Ảnh seed (avatar, ảnh quán, ảnh món) upload lên Cloudinary vào thư mục angi/seed/ với public_id cố định và overwrite = false để chạy lại không tạo ảnh trùng; media_files trỏ đúng url đó. Chỉ dùng ảnh tự chụp hoặc có giấy phép dùng lại. | Làm sau: Database: ANGIContext schema core, base class, initial migration.</t>
+          <t>Dữ liệu đúng cấu trúc ANGI_Data_Dictionary_Ver1.2, chạy lại được nhiều lần. Đủ để test Discovery và Roadmap trước khi có Moderation (Iteration 3); mỗi role có ít nhất 1 tài khoản test. Mọi quán phải có tọa độ thật (latitude/longitude bắt buộc); mỗi tỉnh test có quán ở vài phường/xã khác nhau để thử lọc quán gần, gom cụm theo ngày và route Mapbox. Mỗi món có mô tả rõ vị (30..2000 ký tự) vì reco sinh dish vector từ tên + mô tả. Ảnh seed (avatar, ảnh quán, ảnh món) upload lên Cloudinary vào thư mục angi/seed/ với public_id cố định và overwrite = false để chạy lại không tạo ảnh trùng; media_files trỏ đúng url đó. Chỉ dùng ảnh tự chụp hoặc có giấy phép dùng lại. | Làm sau: Database: ANGIContext schema core, base class, initial migration.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">

--- a/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
+++ b/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Dữ liệu đúng cấu trúc ANGI_Data_Dictionary_Ver1.2, chạy lại được nhiều lần. Đủ để test Discovery và Roadmap trước khi có Moderation (Iteration 3); mỗi role có ít nhất 1 tài khoản test. Mọi quán phải có tọa độ thật (latitude/longitude bắt buộc); mỗi tỉnh test có quán ở vài phường/xã khác nhau để thử lọc quán gần, gom cụm theo ngày và route Mapbox. Mỗi món có mô tả rõ vị (30..2000 ký tự) vì reco sinh dish vector từ tên + mô tả. Ảnh seed (avatar, ảnh quán, ảnh món) upload lên Cloudinary vào thư mục angi/seed/ với public_id cố định và overwrite = false để chạy lại không tạo ảnh trùng; media_files trỏ đúng url đó. Chỉ dùng ảnh tự chụp hoặc có giấy phép dùng lại. | Làm sau: Database: ANGIContext schema core, base class, initial migration.</t>
+          <t>Dữ liệu đúng cấu trúc ANGI_Data_Dictionary_Ver1.2, chạy lại được nhiều lần. Đủ để test Discovery và Roadmap trước khi có Moderation (Iteration 3); mỗi role có ít nhất 1 tài khoản test. Mọi quán phải có tọa độ thật (latitude/longitude bắt buộc); mỗi tỉnh test có quán ở vài phường/xã khác nhau (tên tỉnh và phường/xã theo provinces.open-api.vn V2) để thử lọc quán gần, gom cụm theo ngày và route Mapbox. Mỗi món có mô tả rõ vị (30..2000 ký tự) vì reco sinh dish vector từ tên + mô tả. Ảnh seed (avatar, ảnh quán, ảnh món) upload lên Cloudinary vào thư mục angi/seed/ với public_id cố định và overwrite = false để chạy lại không tạo ảnh trùng; media_files trỏ đúng url đó. Chỉ dùng ảnh tự chụp hoặc có giấy phép dùng lại. | Làm sau: Database: ANGIContext schema core, base class, initial migration.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">

--- a/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
+++ b/.docs/ANGI_Jira_Plan_Ver1.2.xlsx
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Dữ liệu đúng cấu trúc ANGI_Data_Dictionary_Ver1.2, chạy lại được nhiều lần. Đủ để test Discovery và Roadmap trước khi có Moderation (Iteration 3); mỗi role có ít nhất 1 tài khoản test. Mọi quán phải có tọa độ thật (latitude/longitude bắt buộc); mỗi tỉnh test có quán ở vài quận khác nhau để thử lọc quán gần, gom cụm theo ngày và route Mapbox. Mỗi món có mô tả rõ vị (30..2000 ký tự) vì reco sinh dish vector từ tên + mô tả. Ảnh seed (avatar, ảnh quán, ảnh món) upload lên Cloudinary vào thư mục angi/seed/ với public_id cố định và overwrite = false để chạy lại không tạo ảnh trùng; media_files trỏ đúng url đó. Chỉ dùng ảnh tự chụp hoặc có giấy phép dùng lại. | Làm sau: Database: ANGIContext schema core, base class, initial migration.</t>
+          <t>Dữ liệu đúng cấu trúc ANGI_Data_Dictionary_Ver1.2, chạy lại được nhiều lần. Đủ để test Discovery và Roadmap trước khi có Moderation (Iteration 3); mỗi role có ít nhất 1 tài khoản test. Mọi quán phải có tọa độ thật (latitude/longitude bắt buộc); mỗi tỉnh test có quán ở vài phường/xã khác nhau (tên tỉnh và phường/xã theo provinces.open-api.vn V2) để thử lọc quán gần, gom cụm theo ngày và route Mapbox. Mỗi món có mô tả rõ vị (30..2000 ký tự) vì reco sinh dish vector từ tên + mô tả. Ảnh seed (avatar, ảnh quán, ảnh món) upload lên Cloudinary vào thư mục angi/seed/ với public_id cố định và overwrite = false để chạy lại không tạo ảnh trùng; media_files trỏ đúng url đó. Chỉ dùng ảnh tự chụp hoặc có giấy phép dùng lại. | Làm sau: Database: ANGIContext schema core, base class, initial migration.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
